--- a/nozzle_catalog.xlsx
+++ b/nozzle_catalog.xlsx
@@ -436,16 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
         <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11</v>
+        <v>0.51</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -536,7 +536,7 @@
         <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
@@ -567,7 +567,7 @@
         <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>0.41</v>
+        <v>1.98</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -598,7 +598,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>0.53</v>
+        <v>2.53</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -629,7 +629,7 @@
         <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>0.11</v>
+        <v>0.51</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -660,7 +660,7 @@
         <v>30</v>
       </c>
       <c r="E7" t="n">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -691,7 +691,7 @@
         <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>0.33</v>
+        <v>1.58</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -722,7 +722,7 @@
         <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>0.53</v>
+        <v>2.53</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -753,7 +753,7 @@
         <v>30</v>
       </c>
       <c r="E10" t="n">
-        <v>0.82</v>
+        <v>3.95</v>
       </c>
       <c r="F10" t="n">
         <v>5</v>
@@ -784,7 +784,7 @@
         <v>30</v>
       </c>
       <c r="E11" t="n">
-        <v>1.32</v>
+        <v>6.33</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
@@ -815,7 +815,7 @@
         <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>2.07</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -846,7 +846,7 @@
         <v>30</v>
       </c>
       <c r="E13" t="n">
-        <v>2.63</v>
+        <v>12.65</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -877,7 +877,7 @@
         <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>3.29</v>
+        <v>15.81</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
@@ -908,7 +908,7 @@
         <v>45</v>
       </c>
       <c r="E15" t="n">
-        <v>0.11</v>
+        <v>0.51</v>
       </c>
       <c r="F15" t="n">
         <v>5</v>
@@ -939,7 +939,7 @@
         <v>45</v>
       </c>
       <c r="E16" t="n">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -970,7 +970,7 @@
         <v>45</v>
       </c>
       <c r="E17" t="n">
-        <v>0.33</v>
+        <v>1.58</v>
       </c>
       <c r="F17" t="n">
         <v>5</v>
@@ -1001,7 +1001,7 @@
         <v>45</v>
       </c>
       <c r="E18" t="n">
-        <v>0.53</v>
+        <v>2.53</v>
       </c>
       <c r="F18" t="n">
         <v>5</v>
@@ -1032,7 +1032,7 @@
         <v>45</v>
       </c>
       <c r="E19" t="n">
-        <v>0.82</v>
+        <v>3.95</v>
       </c>
       <c r="F19" t="n">
         <v>5</v>
@@ -1063,7 +1063,7 @@
         <v>45</v>
       </c>
       <c r="E20" t="n">
-        <v>1.32</v>
+        <v>6.33</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -1094,7 +1094,7 @@
         <v>45</v>
       </c>
       <c r="E21" t="n">
-        <v>2.07</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F21" t="n">
         <v>5</v>
@@ -1125,7 +1125,7 @@
         <v>45</v>
       </c>
       <c r="E22" t="n">
-        <v>2.63</v>
+        <v>12.65</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
@@ -1156,7 +1156,7 @@
         <v>45</v>
       </c>
       <c r="E23" t="n">
-        <v>3.29</v>
+        <v>15.81</v>
       </c>
       <c r="F23" t="n">
         <v>5</v>
@@ -1187,7 +1187,7 @@
         <v>60</v>
       </c>
       <c r="E24" t="n">
-        <v>0.11</v>
+        <v>0.51</v>
       </c>
       <c r="F24" t="n">
         <v>5</v>
@@ -1218,7 +1218,7 @@
         <v>60</v>
       </c>
       <c r="E25" t="n">
-        <v>0.15</v>
+        <v>0.71</v>
       </c>
       <c r="F25" t="n">
         <v>5</v>
@@ -1249,7 +1249,7 @@
         <v>60</v>
       </c>
       <c r="E26" t="n">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
         <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>0.33</v>
+        <v>1.58</v>
       </c>
       <c r="F27" t="n">
         <v>5</v>
@@ -1311,7 +1311,7 @@
         <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>0.41</v>
+        <v>1.98</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
@@ -1342,7 +1342,7 @@
         <v>60</v>
       </c>
       <c r="E29" t="n">
-        <v>0.53</v>
+        <v>2.53</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
@@ -1373,7 +1373,7 @@
         <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>0.62</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
         <v>5</v>
@@ -1404,7 +1404,7 @@
         <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>0.82</v>
+        <v>3.95</v>
       </c>
       <c r="F31" t="n">
         <v>5</v>
@@ -1435,7 +1435,7 @@
         <v>60</v>
       </c>
       <c r="E32" t="n">
-        <v>1.04</v>
+        <v>4.98</v>
       </c>
       <c r="F32" t="n">
         <v>5</v>
@@ -1466,7 +1466,7 @@
         <v>60</v>
       </c>
       <c r="E33" t="n">
-        <v>1.32</v>
+        <v>6.33</v>
       </c>
       <c r="F33" t="n">
         <v>5</v>
@@ -1497,7 +1497,7 @@
         <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>1.56</v>
+        <v>7.51</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -1528,7 +1528,7 @@
         <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>2.07</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F35" t="n">
         <v>5</v>
@@ -1559,7 +1559,7 @@
         <v>60</v>
       </c>
       <c r="E36" t="n">
-        <v>2.63</v>
+        <v>12.65</v>
       </c>
       <c r="F36" t="n">
         <v>5</v>
@@ -1590,7 +1590,7 @@
         <v>60</v>
       </c>
       <c r="E37" t="n">
-        <v>3.29</v>
+        <v>15.81</v>
       </c>
       <c r="F37" t="n">
         <v>5</v>
@@ -1621,7 +1621,7 @@
         <v>60</v>
       </c>
       <c r="E38" t="n">
-        <v>4.11</v>
+        <v>19.76</v>
       </c>
       <c r="F38" t="n">
         <v>5</v>
@@ -1652,7 +1652,7 @@
         <v>60</v>
       </c>
       <c r="E39" t="n">
-        <v>5.26</v>
+        <v>25.3</v>
       </c>
       <c r="F39" t="n">
         <v>5</v>
@@ -1683,7 +1683,7 @@
         <v>75</v>
       </c>
       <c r="E40" t="n">
-        <v>0.017</v>
+        <v>0.08</v>
       </c>
       <c r="F40" t="n">
         <v>5</v>
@@ -1714,7 +1714,7 @@
         <v>75</v>
       </c>
       <c r="E41" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="F41" t="n">
         <v>5</v>
@@ -1745,7 +1745,7 @@
         <v>75</v>
       </c>
       <c r="E42" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="F42" t="n">
         <v>5</v>
@@ -1776,7 +1776,7 @@
         <v>75</v>
       </c>
       <c r="E43" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="F43" t="n">
         <v>5</v>
@@ -1807,7 +1807,7 @@
         <v>75</v>
       </c>
       <c r="E44" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="F44" t="n">
         <v>5</v>
@@ -1838,7 +1838,7 @@
         <v>75</v>
       </c>
       <c r="E45" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="F45" t="n">
         <v>5</v>
@@ -1869,7 +1869,7 @@
         <v>90</v>
       </c>
       <c r="E46" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="F46" t="n">
         <v>5</v>
@@ -1900,7 +1900,7 @@
         <v>90</v>
       </c>
       <c r="E47" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="F47" t="n">
         <v>5</v>
@@ -1931,7 +1931,7 @@
         <v>90</v>
       </c>
       <c r="E48" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="F48" t="n">
         <v>5</v>
@@ -1962,7 +1962,7 @@
         <v>90</v>
       </c>
       <c r="E49" t="n">
-        <v>0.11</v>
+        <v>0.51</v>
       </c>
       <c r="F49" t="n">
         <v>5</v>
@@ -1993,7 +1993,7 @@
         <v>90</v>
       </c>
       <c r="E50" t="n">
-        <v>0.15</v>
+        <v>0.71</v>
       </c>
       <c r="F50" t="n">
         <v>5</v>
@@ -2024,7 +2024,7 @@
         <v>90</v>
       </c>
       <c r="E51" t="n">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
         <v>5</v>
@@ -2055,7 +2055,7 @@
         <v>90</v>
       </c>
       <c r="E52" t="n">
-        <v>0.33</v>
+        <v>1.58</v>
       </c>
       <c r="F52" t="n">
         <v>5</v>
@@ -2086,7 +2086,7 @@
         <v>90</v>
       </c>
       <c r="E53" t="n">
-        <v>0.41</v>
+        <v>1.98</v>
       </c>
       <c r="F53" t="n">
         <v>5</v>
@@ -2117,7 +2117,7 @@
         <v>90</v>
       </c>
       <c r="E54" t="n">
-        <v>0.53</v>
+        <v>2.53</v>
       </c>
       <c r="F54" t="n">
         <v>5</v>
@@ -2148,7 +2148,7 @@
         <v>90</v>
       </c>
       <c r="E55" t="n">
-        <v>0.62</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>5</v>
@@ -2179,7 +2179,7 @@
         <v>90</v>
       </c>
       <c r="E56" t="n">
-        <v>0.82</v>
+        <v>3.95</v>
       </c>
       <c r="F56" t="n">
         <v>5</v>
@@ -2210,7 +2210,7 @@
         <v>90</v>
       </c>
       <c r="E57" t="n">
-        <v>1.04</v>
+        <v>4.98</v>
       </c>
       <c r="F57" t="n">
         <v>5</v>
@@ -2241,7 +2241,7 @@
         <v>90</v>
       </c>
       <c r="E58" t="n">
-        <v>1.32</v>
+        <v>6.33</v>
       </c>
       <c r="F58" t="n">
         <v>5</v>
@@ -2272,7 +2272,7 @@
         <v>90</v>
       </c>
       <c r="E59" t="n">
-        <v>1.56</v>
+        <v>7.51</v>
       </c>
       <c r="F59" t="n">
         <v>5</v>
@@ -2303,7 +2303,7 @@
         <v>90</v>
       </c>
       <c r="E60" t="n">
-        <v>2.07</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F60" t="n">
         <v>5</v>
@@ -2334,7 +2334,7 @@
         <v>90</v>
       </c>
       <c r="E61" t="n">
-        <v>2.63</v>
+        <v>12.65</v>
       </c>
       <c r="F61" t="n">
         <v>5</v>
@@ -2365,7 +2365,7 @@
         <v>90</v>
       </c>
       <c r="E62" t="n">
-        <v>3.29</v>
+        <v>15.81</v>
       </c>
       <c r="F62" t="n">
         <v>5</v>
@@ -2396,7 +2396,7 @@
         <v>90</v>
       </c>
       <c r="E63" t="n">
-        <v>4.11</v>
+        <v>19.76</v>
       </c>
       <c r="F63" t="n">
         <v>5</v>
@@ -2427,7 +2427,7 @@
         <v>90</v>
       </c>
       <c r="E64" t="n">
-        <v>5.26</v>
+        <v>25.3</v>
       </c>
       <c r="F64" t="n">
         <v>5</v>
@@ -2441,159 +2441,655 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SprayingSystems</t>
+          <t>Lechler</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FullJet</t>
+          <t>652</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>cone</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E65" t="n">
-        <v>12</v>
+        <v>0.13</v>
       </c>
       <c r="F65" t="n">
         <v>5</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>FullJet-60-12</t>
+          <t>652.187</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SprayingSystems</t>
+          <t>Lechler</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FullJet</t>
+          <t>652</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>cone</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E66" t="n">
-        <v>20</v>
+        <v>0.18</v>
       </c>
       <c r="F66" t="n">
         <v>5</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>FullJet-60-20</t>
+          <t>652.217</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SprayingSystems</t>
+          <t>Lechler</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FullJet</t>
+          <t>652</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>cone</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E67" t="n">
-        <v>15</v>
+        <v>0.26</v>
       </c>
       <c r="F67" t="n">
         <v>5</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>FullJet-90-15</t>
+          <t>652.247</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SprayingSystems</t>
+          <t>Lechler</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FullJet</t>
+          <t>652</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>cone</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E68" t="n">
-        <v>25</v>
+        <v>0.35</v>
       </c>
       <c r="F68" t="n">
         <v>5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>FullJet-90-25</t>
+          <t>652.277</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>120</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F69" t="n">
+        <v>5</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>652.307</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>120</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F70" t="n">
+        <v>5</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>652.337</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>120</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>652.367</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>120</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F72" t="n">
+        <v>5</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>652.407</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>120</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F73" t="n">
+        <v>5</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>652.447</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>120</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="F74" t="n">
+        <v>5</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>652.487</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>120</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>652.517</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>120</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="F76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>652.567</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>120</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="F77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>652.607</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>120</v>
+      </c>
+      <c r="E78" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="F78" t="n">
+        <v>5</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>652.647</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>120</v>
+      </c>
+      <c r="E79" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>652.677</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>120</v>
+      </c>
+      <c r="E80" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="F80" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>652.727</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>120</v>
+      </c>
+      <c r="E81" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="F81" t="n">
+        <v>5</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>652.767</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>120</v>
+      </c>
+      <c r="E82" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="F82" t="n">
+        <v>5</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>652.807</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>120</v>
+      </c>
+      <c r="E83" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="F83" t="n">
+        <v>5</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>652.847</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Lechler</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>120</v>
+      </c>
+      <c r="E84" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="F84" t="n">
+        <v>5</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>652.887</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>NOTE:</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>type: flat = getto piatto (flat-fan), cone = cono pieno</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>flow_lpm_at_ref = portata L/min alla pressione di riferimento p_ref_bar</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>flow_lpm_at_ref = portata L/min @ p_ref_bar (dati ufficiali Lechler 652 a 5 bar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Legge portata: Q(p) = flow_lpm_at_ref * sqrt(p / p_ref_bar)</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>Per aggiungere ugelli: nuova riga con gli stessi campi. Esporta poi come CSV per il software.</t>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Per aggiungere ugelli: nuova riga, poi esporta come CSV per il software.</t>
         </is>
       </c>
     </row>
